--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0077.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0077.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Excessively Cautious</t>
+          <t>Cảnh Giác Quá Mức</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>I Admit, Bạn Are Strong</t>
+          <t>Ta Thừa Nhận, Ngươi Mạnh Thật</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Unfamiliar Ceiling</t>
+          <t>Trần nhà lạ lẫm</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Practice Makes Perfect</t>
+          <t>Luyện tập tạo nên hoàn hảo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Miễn Là Có Tác Dụng!</t>
+          <t>Chừng Nào Còn Xài Được!</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Rất Vui Được Gặp Cậu</t>
+          <t>Rất vui được gặp cậu</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Ngươi Là Đầy Tớ Của Ta Sao?</t>
+          <t>Ngươi có phải là kẻ hầu của ta không?</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Golden Legend I</t>
+          <t>Huyền Thoại Vàng I</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Dùng Echo Đánh Bại Echo</t>
+          <t>Đánh bại Echoes bằng Echoes</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Ace Trainer</t>
+          <t>Huấn Luyện Viên Xuất Sắc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Trở Thành Người Đam Mê Echo!</t>
+          <t>Trở thành Người Đam Mê Dư Âm!</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Trở Thành Chuyên Gia Echo!</t>
+          <t>Trở thành Chuyên Gia Dư Âm!</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Trở Thành Bậc Thầy Echo!</t>
+          <t>Trở thành Bậc Thầy Dư Âm!</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Butterfly Effect I</t>
+          <t>Hiệu Ứng Cánh Bướm I</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Butterfly Effect II</t>
+          <t>Hiệu Ứng Cánh Bướm II</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Butterfly Effect III</t>
+          <t>Hiệu Ứng Cánh Bướm III</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Golden Legend II</t>
+          <t>Huyền Thoại Vàng II</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Golden Legend III</t>
+          <t>Huyền Thoại Vàng III</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Nothing Less</t>
+          <t>Không Thể Kém Hơn</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Long Live Friendship</t>
+          <t>Tình Bạn Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Long-Awaited Reunion</t>
+          <t>Cuộc Hội Ngộ Đã Lâu</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Amazing Chemical Reaction</t>
+          <t>Phản Ứng Hóa Học Kỳ Diệu</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>One Mind</t>
+          <t>Đồng Tâm Nhất Trí</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Đây Là Mối Ràng Buộc Của Chúng Ta!</t>
+          <t>Đây là mối liên kết của chúng ta!</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Now Who's Mourning</t>
+          <t>Giờ Ai Đang Than Khóc</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Giành Lại Rừng Mờ!</t>
+          <t>Giải phóng Rừng Tối!</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Let's Be Lost Together</t>
+          <t>Cùng Đi Lạc Lối Nào</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Thiêu Rụi Thành Tro Tàn</t>
+          <t>Hóa tro tàn</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Hóa Thành Tro Bụi</t>
+          <t>Tro Bụi Trở Về Tro Bụi</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Tiếng Chuông Ngân Vì Ai</t>
+          <t>Vì ai ngân vang tiếng chuông</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Thunder Tamer</t>
+          <t>Thuần Hóa Sấm Sét</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Chuyển Ngay!</t>
+          <t>Chuyển ngay!</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Godlike</t>
+          <t>Sức Mạnh Thần Thánh</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Point Zero</t>
+          <t>Điểm Zero</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Điều tra Dị thường</t>
+          <t>Điều tra dị thường</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Đồng bằng Trung tâm</t>
+          <t>Central Plains</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Cao nguyên Desorock</t>
+          <t>Desorock Highland</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Dọn Sạch Bất Kỳ Tacet Field Nào</t>
+          <t>Dọn sạch bất kỳ Tổ Tacet nào</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Đánh bại 5 kẻ địch</t>
+          <t>Tiêu diệt 5 kẻ địch</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Absorb 1 Echo </t>
+          <t>Hấp thu 1 Dư Âm</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Đánh bại 1 kẻ địch Hạng Overlord</t>
+          <t>Đánh bại 1 kẻ địch Cấp Chúa Tể</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Hoàn Thành Thử Thách Mô Phỏng 1 lần</t>
+          <t>Hoàn thành Thử Thách Mô Phỏng 1 lần</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Thu Thập 3 Vật Phẩm Sưu Tầm</t>
+          <t>Thu thập 3 Vật phẩm sưu tầm</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Sử Dụng Synthesizer 1 lần</t>
+          <t>Sử dụng Synthesizer 1 lần</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Tiêu Hao Bất Kỳ Loại Potion Nào 1 lần</t>
+          <t>Dùng 1 Lọ Thuốc bất kỳ.</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Tiêu thụ bất kỳ Món ăn nào 1 lần</t>
+          <t>Dùng bất kỳ món ăn nào 1 lần</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Nhận được 1 miếng Thịt sống</t>
+          <t>Nhận được 1 miếng Thịt Tươi</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Điều chỉnh bất kỳ Echo nào 1 lần</t>
+          <t>Điều chỉnh bất kỳ Echo 1 lần</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Nâng cấp bất kỳ Echo nào 1 lần</t>
+          <t>Nâng cấp Echo bất kỳ 1 lần.</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Nâng cấp bất kỳ Resonator nào 1 lần</t>
+          <t>Nâng cấp Resonator bất kỳ 1 lần.</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Nâng cấp bất kỳ Vũ khí nào 1 lần</t>
+          <t>Nâng cấp Vũ khí bất kỳ 1 lần.</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử thách Rèn luyện 1 lần</t>
+          <t>Hoàn thành Thử Thách Giả Mạo 1 lần</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Sử dụng tổng cộng 10.000 Shell Credit</t>
+          <t>Dùng tổng cộng 10.000 Shell Credits</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Sử dụng tổng cộng 120 Waveplate</t>
+          <t>Dùng tổng cộng 120 Waveplates</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Đạt 100 điểm Hoạt động Sổ tay Hướng dẫn</t>
+          <t>Thu thập 100 Điểm Hoạt Động Sổ Tay Hướng Dẫn</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Đánh bại 5 kẻ địch</t>
+          <t>Tiêu diệt 5 kẻ địch</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Nhận được bất kỳ Echo nào</t>
+          <t>Nhận bất kỳ 1 Echo nào</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Điều chỉnh bất kỳ Echo nào 1 lần</t>
+          <t>Điều chỉnh bất kỳ Echo 1 lần</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Đạt 100 điểm Hoạt động Sổ tay Hướng dẫn</t>
+          <t>Thu thập 100 Điểm Hoạt Động Sổ Tay Hướng Dẫn</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Sử dụng tổng cộng 120 Waveplate</t>
+          <t>Dùng tổng cộng 120 Waveplates</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Đánh bại 1 kẻ địch Hạng Overlord</t>
+          <t>Đánh bại 1 kẻ địch Cấp Chúa Tể</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Điều tra Tacet Field tái xuất hiện</t>
+          <t>Kiểm tra Tổ Tacet tái xuất hiện</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Quan sát các TD còn sót lại</t>
+          <t>Hãy quan sát những Tacet Discord còn vương vấn</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Tìm hiểu thêm về TD mạnh mẽ</t>
+          <t>Tìm hiểu thêm về TD hùng mạnh</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Tăng cường sức mạnh cho các trận chiến</t>
+          <t>Hãy tôi luyện bản thân để sẵn sàng chiến đấu.</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Chuẩn bị cho những cuộc phiêu lưu</t>
+          <t>Chuẩn bị tinh thần cho những chuyến phiêu lưu nào</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Chăm sóc vết thương kịp thời</t>
+          <t>Hãy chữa trị vết thương kịp thời nhé.</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Thưởng thức những món ăn ngon</t>
+          <t>Hãy tự thưởng cho mình một bữa ăn ngon đi</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Chuẩn bị cho những cuộc phiêu lưu</t>
+          <t>Chuẩn bị tinh thần cho những chuyến phiêu lưu nào</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Tăng cường sức mạnh cho các trận chiến</t>
+          <t>Hãy tôi luyện bản thân để sẵn sàng chiến đấu.</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Tăng cường sức mạnh cho các trận chiến</t>
+          <t>Hãy tôi luyện bản thân để sẵn sàng chiến đấu.</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Tăng cường sức mạnh cho các trận chiến</t>
+          <t>Hãy tôi luyện bản thân để sẵn sàng chiến đấu.</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Tăng cường sức mạnh cho các trận chiến</t>
+          <t>Hãy tôi luyện bản thân để sẵn sàng chiến đấu.</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Chuẩn bị vật tư cần thiết cho cuộc khảo sát</t>
+          <t>Chuẩn bị đủ vật tư cho cuộc khảo sát</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Đóng vai trò tích cực trong các hoạt động khảo sát</t>
+          <t>Tham gia tích cực vào các hoạt động khảo sát</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Đóng vai trò tích cực trong các hoạt động khảo sát</t>
+          <t>Tham gia tích cực vào các hoạt động khảo sát</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Đóng vai trò tích cực trong các hoạt động khảo sát</t>
+          <t>Tham gia tích cực vào các hoạt động khảo sát</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Quan sát Tacet Discord Tồn Tại</t>
+          <t>Quan sát Lingering TD</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Ghi lại tần suất của Tacet Discord</t>
+          <t>Ghi lại tần số của TD</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Tăng cường sức mạnh cho các trận chiến</t>
+          <t>Hãy tôi luyện bản thân để sẵn sàng chiến đấu.</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Tìm hiểu thêm về Tacet Discord mạnh mẽ</t>
+          <t>Tìm hiểu thêm về TD hùng mạnh</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Swift Dog</t>
+          <t>Chó Nhanh</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Animals</t>
+          <t>Động vật</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Fighting Dog</t>
+          <t>Chó Chiến</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Animals</t>
+          <t>Động vật</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Green Rabbit</t>
+          <t>Thỏ Xanh</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Animals</t>
+          <t>Động vật</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Animals</t>
+          <t>Động vật</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Gray Ridge Bull</t>
+          <t>Bò Xám Vách Núi</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Animals</t>
+          <t>Động vật</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Morri Cow</t>
+          <t>Bò Morri</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Animals</t>
+          <t>Động vật</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Cá</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Frostwing</t>
+          <t>Đôi Cánh Băng Giá</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Bird</t>
+          <t>Chim</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Silver-Banded Lizard</t>
+          <t>Thằn Lằn Vằn Bạc</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Reptile</t>
+          <t>Loài Bò Sát</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Azure Lizard</t>
+          <t>Thằn Lằn Lam</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Reptile</t>
+          <t>Loài Bò Sát</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Green Pit Lizard</t>
+          <t>Thằn Lằn Hố Xanh</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Reptile</t>
+          <t>Loài Bò Sát</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Black-Striped Frog</t>
+          <t>Ếch Sọc Đen</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Reptile</t>
+          <t>Loài Bò Sát</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Goldenback Frog</t>
+          <t>Ếch Lưng Vàng</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Reptile</t>
+          <t>Loài Bò Sát</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Phoenix Butterfly</t>
+          <t>Bướm Phượng Hoàng</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Insect</t>
+          <t>Côn Trùng</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Red Feather Butterfly</t>
+          <t>Bướm Đỏ Lông Vũ</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Insect</t>
+          <t>Côn Trùng</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Blue Feather Butterfly</t>
+          <t>Bướm Lông Xanh</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Insect</t>
+          <t>Côn Trùng</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Insect</t>
+          <t>Côn Trùng</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Bird</t>
+          <t>Chim</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Golden-ringed Dragonfly</t>
+          <t>Chuồn Chuồn Vàng Vòng</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Insect</t>
+          <t>Côn Trùng</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Eveflitter</t>
+          <t>Bươm Bướm Đêm</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Bird</t>
+          <t>Chim</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Gray Crested Gull</t>
+          <t>Mòng Biển Đỉnh Xám</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Bird</t>
+          <t>Chim</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Snow Crane</t>
+          <t>Hạc Tuyết</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Bird</t>
+          <t>Chim</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Tricolor</t>
+          <t>Ba Màu</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Animals</t>
+          <t>Động vật</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Animals</t>
+          <t>Động vật</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Snowwhite</t>
+          <t>Bạch Tuyết</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Animals</t>
+          <t>Động vật</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Dim Forest Investigation Report</t>
+          <t>Báo Cáo Điều Tra Rừng U Tối</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Misty Deep Pit Exploration Record</t>
+          <t>Bản Ghi Khám Phá Hố Sâu Sương Mù</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Battlefield Record</t>
+          <t>Biên bản chiến trường</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Mala Beads</t>
+          <t>Tràng Hạt Mala</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>The Amorphous</t>
+          <t>Vô Hình</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Simplistic Rings</t>
+          <t>Nhẫn Đơn Giản</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Miniature You'tan</t>
+          <t>Bản sao You'tan thu nhỏ</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Huy chương Danh dự</t>
+          <t>Huy Chương Danh Dự</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Liondance Head</t>
+          <t>Đầu Sư Tử Múa</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Jinzhou Skewers</t>
+          <t>Xiên Nướng Jinzhou</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Worn Longevity Lock</t>
+          <t>Ổ Khóa Trường Thọ Cũ</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Headline Screenshots</t>
+          <t>Ảnh chụp tiêu đề</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Huy hiệu Anh hùng</t>
+          <t>Huy Hiệu Anh Hùng</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Wooly Dolls</t>
+          <t>Búp Bê Wooly</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Coral Bowl</t>
+          <t>Bát San Hô</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Prank Toy</t>
+          <t>Đồ chơi chơi khăm</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Emotion Switch</t>
+          <t>Chuyển đổi cảm xúc</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Homemade Candy</t>
+          <t>Kẹo Nhà Làm</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Shattered Skies</t>
+          <t>Bầu Trời Vỡ Tan</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>The Underdog's Nameplate</t>
+          <t>Bảng Tên Kẻ Dưới Đáy</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Military Rations</t>
+          <t>Lương Khô Quân Dụng</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Broken Fang</t>
+          <t>Nanh Gãy</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Zapstring the Puppet</t>
+          <t>Dây Sét – Con Rối</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Sách về Qipao</t>
+          <t>Sách về Sườn Xám</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Magnifying Glass</t>
+          <t>Kính Lúp</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Dried Fish</t>
+          <t>Cá khô</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Blue Flask</t>
+          <t>Bình Thủy Tinh Xanh</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Old Gauntlet</t>
+          <t>Băng Tay Cổ</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Loong Bun</t>
+          <t>Bánh Lồng Đèn</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>To-do List</t>
+          <t>Danh sách việc cần làm</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Loong Scale</t>
+          <t>Vảy Rồng</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Striped Ribbon</t>
+          <t>Ruy Băng Kẻ Sọc</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Sound Recorder</t>
+          <t>Máy ghi Âm</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Tất Cả Trong Một</t>
+          <t>Tất cả trong Một</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Wind Chimes</t>
+          <t>Chuông gió</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Intelligence Network</t>
+          <t>Mạng Lưới Tình Báo</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Vintage Console</t>
+          <t>Máy chơi game cổ điển</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Binh Pháp</t>
+          <t>Nghệ Thuật Chiến Tranh</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Medicine Box</t>
+          <t>Hộp Thuốc</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Một Góc Jinzhou</t>
+          <t>Một Góc Phố Jinzhou</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Gương Sáng</t>
+          <t>Gương Sáng Tâm Minh</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Coupon Clip</t>
+          <t>Phiếu Giảm Giá</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Velvet Grass</t>
+          <t>Cỏ Nhung</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Expedition Goggles</t>
+          <t>Kính Bảo Hộ Thám Hiểm</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Vĩnh Cửu Trong Hoa</t>
+          <t>Vĩnh Cửu Nở Rộ</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Ghi Chép Thám Hiểm Hoang Dã</t>
+          <t>Ghi chép về Thám Hiểm Vùng Hoang Dã</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Guardian Wall Model</t>
+          <t>Mô hình Tường Bảo Vệ</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Jinzhou Strategies</t>
+          <t>Binh pháp Tấn Châu</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Peachy Turtle</t>
+          <t>Rùa Đào</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Silky Reveries</t>
+          <t>Mộng Ảo Tơ Trời</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Hand Mirror</t>
+          <t>Gương Tay Cầm</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Jade Pendant</t>
+          <t>Mặt dây chuyền Jade</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Firmament Weiqi Manual</t>
+          <t>Cẩm nang Cờ Vây Firmament</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Flame-Soaked Cloth</t>
+          <t>Mảnh Vải Ngấm Lửa</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Blaze Feather</t>
+          <t>Lông Vũ Blaze</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Snow Waltz</t>
+          <t>Điệu Valse Tuyết</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Healing You'tan</t>
+          <t>Hồi phục You'tan</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Frosty Gusto</t>
+          <t>Hơi Thở Băng Giá</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Gallant Blaze</t>
+          <t>Lửa Dũng Mãnh</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>New Federation</t>
+          <t>Liên Bang Mới</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Wooly-Counting Game</t>
+          <t>Trò Đếm Cừu Wooly</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>New Federation</t>
+          <t>Liên Bang Mới</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Dragon's Breath</t>
+          <t>Hơi Thở Rồng</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>New Federation</t>
+          <t>Liên Bang Mới</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>"Ghost Hounds"</t>
+          <t>"Lũ Chó Ma"</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Phantom Hunter</t>
+          <t>Thợ Săn Ảo Ảnh</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Enforcer Puppet</t>
+          <t>Bù Nhìn Thực Thi</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Ngày 2 tháng 10</t>
+          <t>Ngày 2 tháng Mười</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Fist of Thunder</t>
+          <t>Nắm Đấm Sấm Sét</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Ngày 11 tháng 10</t>
+          <t>Ngày 11 tháng Mười</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Breath of Winds</t>
+          <t>Hơi Gió Thổi</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>New Federation</t>
+          <t>Liên Bang Mới</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Mistcloak Strike</t>
+          <t>Đòn Đánh Áo Sương</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Windborne Rider</t>
+          <t>Kỵ Sĩ Gió Bay</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Cleansing Reflections</t>
+          <t>Những Phản Chiếu Thanh Tẩy</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Nam</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Ngày 18 tháng 5</t>
+          <t>Ngày 18 tháng Năm</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>New Federation</t>
+          <t>Liên Bang Mới</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Nature Calling</t>
+          <t>Tiếng Gọi Của Tự Nhiên</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Blossom of Slashes</t>
+          <t>Lưỡi Kiếm Nở Hoa</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Scarlet Shade</t>
+          <t>Bóng Đỏ Thẫm</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Sanguine Blossom</t>
+          <t>Hoa Huyết</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Thawborn Renewal</t>
+          <t>Sự Hồi Sinh Của Băng Giá</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Eternal Blaze</t>
+          <t>Lửa Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Jiang Yue</t>
+          <t>Khương Nguyệt</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Mufei</t>
+          <t>Mộ Phi</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>The Magistrate's Bodyguard</t>
+          <t>Vệ Sĩ của Thị Trưởng</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Sudden Snowfall</t>
+          <t>Tuyết Rơi Bất Chợt</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Lingering Coldness</t>
+          <t>Hàn Khí Lưu Luyến</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Falling Petals</t>
+          <t>Cánh Hoa Rơi</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Thawing Frost</t>
+          <t>Sương Giá Tan Chảy</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Nguyên Tắc Đơn Giản</t>
+          <t>Nguyên Lý Giản Đơn</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Gần Vô Cực</t>
+          <t>Vô Cực Cận Không</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>The Endpoint</t>
+          <t>Điểm Dừng Chân</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Auspicious "Lion Head"</t>
+          <t>Đầu Sư Tử Cát Tường</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Sự Trớ Trêu Của Số Phận</t>
+          <t>Sự Trớ Trêu Của Số Mệnh</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>A Helpful Lion</t>
+          <t>Sư Tử Hữu Ích</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>A Lone Journey</t>
+          <t>Hành Trình Cô Đơn</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>The Naming Ngày</t>
+          <t>Ngày Đặt Tên</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Morning Routine</t>
+          <t>Thói Quen Buổi Sáng</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>The Famous Hero</t>
+          <t>Anh Hùng Nổi Tiếng</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Ignite the Shadows</t>
+          <t>Thắp lên bóng tối.</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Rooftop Encounter</t>
+          <t>Cuộc Gặp Gỡ Trên Sân Thượng</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Thunder and Flames</t>
+          <t>Sấm Sét và Lửa Băng</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Hãy làm bạn nhé!</t>
+          <t>Chúng ta làm bạn nhé!</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Đứa trẻ từ Nhà hát</t>
+          <t>Một Đứa Trẻ Từ Nhà Hát</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>A Heroine's Return</t>
+          <t>Sự Trở Lại Của Nữ Anh Hùng</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Trại trẻ mồ côi và Ngôi nhà Kẹo</t>
+          <t>Trại Trẻ Mồ Côi và Ngôi Nhà Kẹo</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Câu chuyện mới, Cuộc phiêu lưu mới</t>
+          <t>Câu Chuyện Mới, Hành Trình Mới</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>The International Nghiên cứu Fellow</t>
+          <t>Nghiên cứu viên Quốc tế</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Nghệ thuật Ngôn ngữ</t>
+          <t>Nghệ Thuật Ngôn Từ</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>The Tender Grump</t>
+          <t>Kẻ Cộc cằn Dịu Dàng</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Vương miện Tài năng Vỡ vụn</t>
+          <t>Vương Miện Thiên Tài Vỡ Tan</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>The "Magic"</t>
+          <t>"Phép Màu"</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>"Những Con chó Chiến tranh"</t>
+          <t>"Lũ Chó Chiến"</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Quid Pro Quo</t>
+          <t>Có qua có lại</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Beast Instict</t>
+          <t>Bản Năng Thú</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Let Sleeping Dogs Lie</t>
+          <t>Để chó ngủ yên</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Domestication</t>
+          <t>Thuần Hóa</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Đỏ thẫm trong Bóng tối</t>
+          <t>Scarlet Trong Bóng Tối</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>The Puppet Show</t>
+          <t>Múa Rối</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Names Born From Ashes</t>
+          <t>Những Cái Tên Sinh Ra Từ Tro Tàn</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Giã từ Quá khứ</t>
+          <t>Tạm biệt quá khứ</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Góc tối</t>
+          <t>Góc Tối</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Popular Boxing Gym</t>
+          <t>Phòng tập Boxing Nổi tiếng</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Bad Bargain</t>
+          <t>Thỏa thuận tồi</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Tia chớp trên Sân khấu</t>
+          <t>Tia Chớp Trên Sân Khấu</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Soothing Tea</t>
+          <t>Trà Thư Giãn</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Timeless Heritage</t>
+          <t>Di Sản Vượt Thời Gian</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Bí quyết của Sự xuất sắc</t>
+          <t>Bí quyết của sự xuất chúng</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Bí quyết của Việc lắng nghe</t>
+          <t>Bí quyết của lắng nghe</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Bí quyết của Niềm tin</t>
+          <t>Bí quyết của niềm tin</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>What Wind Taught Her</t>
+          <t>Những Điều Gió Đã Dạy Nàng</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Câu trả lời Nằm trong Gió</t>
+          <t>Lời Đáp Trong Gió</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>A Bad Deal</t>
+          <t>Một Thỏa Thuận Tồi</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>A Fair Exchange</t>
+          <t>Một Sự Trao Đổi Công Bằng</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>A Perfect Duo</t>
+          <t>Bộ Đôi Hoàn Hảo</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Một dịch vụ miễn phí</t>
+          <t>Dịch vụ miễn phí thôi mà</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Tưới hoa đi, Khách quý</t>
+          <t>Tưới hoa đi, Quý Khách</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>The Unyielding Will</t>
+          <t>Ý Chí Bất Khuất</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Silent Caretaker</t>
+          <t>Người Trông Nom Im Lặng</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Bên trong Quả bầu của cậu ta có gì?</t>
+          <t>Bên Trong Quả Bầu Của Ông Ấy là gì?</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>The Temporary Đội</t>
+          <t>Đội Hình Tạm Thời</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Linh hồn Thuần khiết của Rừng xanh</t>
+          <t>Linh Hồn Thuần Khiết Của Rừng Xanh</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Innocent Heart's Valor</t>
+          <t>Dũng Khí Của Trái Tim Ngây Thơ</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Bàn tay Nhân từ của Ân điển</t>
+          <t>Bàn Tay Ân Sủng Nhân Từ</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Dilligent Devotion</t>
+          <t>Cống Hiến Tận Tâm</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Mushrooms 101</t>
+          <t>Nấm Cơ Bản 101</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Cultivating Flowers</t>
+          <t>Nuôi Dưỡng Hoa</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Ghi nhận Sự khác biệt</t>
+          <t>Ghi Nhận Sự Khác Biệt</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Những Khoảnh khắc Đau buồn</t>
+          <t>Khoảnh khắc đau thương</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>A Little Time Off</t>
+          <t>Thời Gian Nghỉ Ngơi Ngắn Ngủi</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Prisoner's Dilemma</t>
+          <t>Thế Lưỡng Nan Của Tù Nhân</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Taoqi's Tempo</t>
+          <t>Nhịp điệu của Taoqi</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Taoqi's Time</t>
+          <t>Thời gian của Taoqi</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Sum họp cùng Bạn bè</t>
+          <t>Đoàn tụ cùng Bạn Bè</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Work-life Balance</t>
+          <t>Cân bằng công việc - cuộc sống</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Một Vị Khách Lạ</t>
+          <t>Một Vị Khách Kỳ Lạ</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Special Loong Whisker Crisps</t>
+          <t>Bánh Quế Râu Long Đặc Biệt</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Con Mồi Hay Thợ Săn?</t>
+          <t>Con mồi hay Thợ săn?</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Moonlit Determination</t>
+          <t>Quyết Tâm Dưới Trăng</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Her Leadership</t>
+          <t>Khả Năng Lãnh Đạo Của Nàng</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Her Wish-granting Magic</t>
+          <t>Phép Thuật Ban Ước Của Nàng</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Her Kindness</t>
+          <t>Lòng Tốt Của Nàng</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Her Rare Anger</t>
+          <t>Cơn Giận Hiếm Có Của Nàng</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Her Long-awaited Guest</t>
+          <t>Vị Khách Đã Đợi Lâu</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Chủ Tể và Bầy Tôi</t>
+          <t>Quân Thần</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Chiếc Lông Cô Đơn Trong Ngõ</t>
+          <t>Chiếc Lông Vũ Cô Đơn Trong Ngõ</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Sự Trở lại của Radiance</t>
+          <t>Sự Trở Lại Của Ánh Sáng</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>The Myth-Laden Savior</t>
+          <t>Vị Cứu Tinh Huyền Thoại</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
